--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\MD\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B22D3C2-F9E7-4EEF-AC87-E83AA2134C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52345A83-5F68-4A0A-9840-96C0DE3B94D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="1970" yWindow="2020" windowWidth="14400" windowHeight="7350" firstSheet="2" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Source: </t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>CSC Capacity Supply Curve Share of Cost Effective Capacity Built in a Single Year</t>
+  </si>
+  <si>
+    <t>Maryland</t>
   </si>
 </sst>
 </file>
@@ -184,9 +187,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,25 +505,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -543,12 +553,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -595,7 +605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -653,17 +663,17 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -682,12 +692,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -782,7 +792,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -877,7 +887,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -972,7 +982,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1067,7 +1077,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1162,7 +1172,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1257,102 +1267,102 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="K7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="P7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Q7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="S7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="V7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="X7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Y7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Z7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AA7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AB7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AC7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AD7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AE7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1447,7 +1457,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1542,7 +1552,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1637,7 +1647,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1732,7 +1742,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1827,7 +1837,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1922,7 +1932,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2017,7 +2027,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2112,7 +2122,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2207,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2302,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2397,7 +2407,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2492,7 +2502,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2587,7 +2597,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2682,7 +2692,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2777,7 +2787,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2872,7 +2882,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -2967,7 +2977,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>30</v>
       </c>
